--- a/survey_templates/036_ai_recruitment_software_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/036_ai_recruitment_software_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1027,8 +1027,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'hr_/_talent_acquisition_manager',_'value':_'hr_manager'}</t>
+          <t>hr_/_talent_acquisition_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'HR / Talent Acquisition Manager', 'value': 'hr_manager'}</t>
+          <t>HR / Talent Acquisition Manager</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'recruiter_/_sourcer',_'value':_'recruiter'}</t>
+          <t>recruiter_/_sourcer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Recruiter / Sourcer', 'value': 'recruiter'}</t>
+          <t>Recruiter / Sourcer</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'it_/_systems_administrator',_'value':_'it_admin'}</t>
+          <t>it_/_systems_administrator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'IT / Systems Administrator', 'value': 'it_admin'}</t>
+          <t>IT / Systems Administrator</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'procurement_/_finance',_'value':_'procurement'}</t>
+          <t>procurement_/_finance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Procurement / Finance', 'value': 'procurement'}</t>
+          <t>Procurement / Finance</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'department_head_(hiring_manager)',_'value':_'dept_head'}</t>
+          <t>department_head_(hiring_manager)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Department Head (Hiring Manager)', 'value': 'dept_head'}</t>
+          <t>Department Head (Hiring Manager)</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'native_integration_available',_'value':_'native'}</t>
+          <t>native_integration_available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Native Integration Available', 'value': 'native'}</t>
+          <t>Native Integration Available</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'api_/_custom_integration_required',_'value':_'api_required'}</t>
+          <t>api_/_custom_integration_required</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'API / Custom Integration Required', 'value': 'api_required'}</t>
+          <t>API / Custom Integration Required</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_compatible',_'value':_'not_compatible'}</t>
+          <t>not_compatible</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Compatible', 'value': 'not_compatible'}</t>
+          <t>Not Compatible</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_robust_features',_'value':_'yes_robust'}</t>
+          <t>yes,_robust_features</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, robust features', 'value': 'yes_robust'}</t>
+          <t>Yes, robust features</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_basic_features',_'value':_'yes_basic'}</t>
+          <t>yes,_basic_features</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, basic features', 'value': 'yes_basic'}</t>
+          <t>Yes, basic features</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'gdpr_compliant',_'value':_'gdpr'}</t>
+          <t>gdpr_compliant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'GDPR Compliant', 'value': 'gdpr'}</t>
+          <t>GDPR Compliant</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'soc_2_certified',_'value':_'soc2'}</t>
+          <t>soc_2_certified</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'SOC 2 Certified', 'value': 'soc2'}</t>
+          <t>SOC 2 Certified</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'eeo_/_ofccp_compliant',_'value':_'eeo'}</t>
+          <t>eeo_/_ofccp_compliant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'EEO / OFCCP Compliant', 'value': 'eeo'}</t>
+          <t>EEO / OFCCP Compliant</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'iso_27001',_'value':_'iso27001'}</t>
+          <t>iso_27001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'ISO 27001', 'value': 'iso27001'}</t>
+          <t>ISO 27001</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'per_seat_/_user',_'value':_'per_user'}</t>
+          <t>per_seat_/_user</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Per Seat / User', 'value': 'per_user'}</t>
+          <t>Per Seat / User</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'per_hire_/_success-based',_'value':_'per_hire'}</t>
+          <t>per_hire_/_success-based</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Per Hire / Success-based', 'value': 'per_hire'}</t>
+          <t>Per Hire / Success-based</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'flat_annual_subscription',_'value':_'flat_annual'}</t>
+          <t>flat_annual_subscription</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Flat Annual Subscription', 'value': 'flat_annual'}</t>
+          <t>Flat Annual Subscription</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'usage-based_(per_application)',_'value':_'usage_based'}</t>
+          <t>usage-based_(per_application)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Usage-based (Per Application)', 'value': 'usage_based'}</t>
+          <t>Usage-based (Per Application)</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'shortlist_for_pilot',_'value':_'shortlist'}</t>
+          <t>shortlist_for_pilot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Shortlist for Pilot', 'value': 'shortlist'}</t>
+          <t>Shortlist for Pilot</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'approved_for_purchase',_'value':_'buy'}</t>
+          <t>approved_for_purchase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Approved for Purchase', 'value': 'buy'}</t>
+          <t>Approved for Purchase</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'hold_/_needs_more_info',_'value':_'hold'}</t>
+          <t>hold_/_needs_more_info</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Hold / Needs more info', 'value': 'hold'}</t>
+          <t>Hold / Needs more info</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'reject',_'value':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Reject', 'value': 'reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
